--- a/selenium-tests/ReconAI_Selenium_E2E_Test_Report_300_TestCases.xlsx
+++ b/selenium-tests/ReconAI_Selenium_E2E_Test_Report_300_TestCases.xlsx
@@ -17,7 +17,7 @@
     <t>RECONAI SURGICAL PLATFORM - AUTOMATED E2E TEST REPORT</t>
   </si>
   <si>
-    <t>Execution Date: 11/8/2026, 9:03:35 am | Environment: Web Local &amp; Supabase Cloud | Total Test Cases: 405</t>
+    <t>Execution Date: 14/8/2026, 9:33:03 am | Environment: Web Local &amp; Supabase Cloud | Total Test Cases: 405</t>
   </si>
   <si>
     <t>TOTAL TEST CASES</t>
@@ -146,7 +146,7 @@
     <t>CRITICAL</t>
   </si>
   <si>
-    <t>2026-08-11T03:33:35.106Z</t>
+    <t>2026-08-14T04:03:03.215Z</t>
   </si>
   <si>
     <t>TC-LOG-002</t>
@@ -272,7 +272,7 @@
     <t>Error: Invalid domain name (Verified by Selenium Driver)</t>
   </si>
   <si>
-    <t>2026-08-11T03:33:35.107Z</t>
+    <t>2026-08-14T04:03:03.216Z</t>
   </si>
   <si>
     <t>TC-LOG-011</t>
